--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="2"/>
     </row>
@@ -1301,7 +1301,7 @@
         <v>0.09</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>-0.01</v>
@@ -1350,7 +1350,7 @@
         <v>0.11</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="42">
@@ -1393,10 +1393,10 @@
         <v>0.31</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="44">
@@ -1416,10 +1416,10 @@
         <v>-0.32</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="45">
@@ -1689,13 +1689,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57">
@@ -1761,10 +1761,10 @@
         <v>-0.39</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="60">
@@ -2037,7 +2037,7 @@
         <v>0.17</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>-0.09</v>
@@ -2313,10 +2313,10 @@
         <v>0.17</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="84">
@@ -2336,10 +2336,10 @@
         <v>-0.29</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="85">
@@ -2362,7 +2362,7 @@
         <v>-0.06</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="86">
@@ -2379,10 +2379,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0.51</v>
@@ -2658,10 +2658,10 @@
         <v>0.06</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="99">
@@ -2684,7 +2684,7 @@
         <v>-0.42</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2773,10 +2773,10 @@
         <v>-0.5</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="104">
@@ -2796,10 +2796,10 @@
         <v>-0.36</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="105">
@@ -2822,7 +2822,7 @@
         <v>-0.09</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="106">
@@ -3003,10 +3003,10 @@
         <v>-0.03</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="114">
@@ -3026,10 +3026,10 @@
         <v>-0.49</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="115">
@@ -3069,13 +3069,13 @@
         <v>18</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="117">
@@ -3121,7 +3121,7 @@
         <v>-0.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="119">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_antofagasta.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
